--- a/presentation/SF1-MPS3/anomalies.xlsx
+++ b/presentation/SF1-MPS3/anomalies.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U91"/>
+  <dimension ref="A1:U108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1716,38 +1716,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13440318</v>
+        <v>13440267</v>
       </c>
       <c r="B15" t="n">
-        <v>4002538082</v>
+        <v>4002538041</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INSPECTION VISUELLE EQUIPEMENT</t>
+          <t>INSPECTION VISUELLE CIRCUIT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OR004002538082</t>
+          <t>OR004002538041</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-LIMBAT-0T7402</t>
+          <t>SF01-PS-PS03-SECGAZ-COMMUN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BAC DE STOCKAGE ACIDE SULFURIQUE T5401B</t>
+          <t>COMMUN SECTION GAZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>S-PC-T5401B</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -1779,7 +1775,7 @@
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q15" s="2" t="n">
         <v>46254</v>
@@ -1805,36 +1801,36 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13440340</v>
+        <v>13440280</v>
       </c>
       <c r="B16" t="n">
-        <v>4002538084</v>
+        <v>4002538044</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>INSPECTION VISUELLE CIRCUIT</t>
+          <t>INSPECTION VISUELLE EQUIPEMENT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OR004002538084</t>
+          <t>OR004002538044</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-LIMBAT-VAPRBP</t>
+          <t>SF01-PS-PS03-SECEAU-0T7104</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CIRCUIT VAPEUR BP LIMITE BATTERIE PSIII</t>
+          <t>BAC D'HYDRAZINE T7104 PSIII</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>S-PC-PSIII-VAPBP</t>
+          <t>S-PC-T7104</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1868,7 +1864,7 @@
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q16" s="2" t="n">
         <v>46254</v>
@@ -1894,10 +1890,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13563230</v>
+        <v>13440317</v>
       </c>
       <c r="B17" t="n">
-        <v>4002654003</v>
+        <v>4002538080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1906,24 +1902,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OR004002654003</t>
+          <t>OR004002538080</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECAIR-0P7322</t>
+          <t>SF01-PS-PS03-LIMBAT-0P5402</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MOTOPOMPE HUILE GRAISSAGE GTS PSIII</t>
+          <t>MOTOPOMPE DRAINAGE ACIDE P5402</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>S-PC-P7322</t>
+          <t>S-PC-P5402</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1953,14 +1949,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>IP1020260904</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>46269</v>
+        <v>46254</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -1983,36 +1979,36 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13563481</v>
+        <v>13440318</v>
       </c>
       <c r="B18" t="n">
-        <v>4002654253</v>
+        <v>4002538082</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OMS_MESURE VIBRATION PALIERS</t>
+          <t>INSPECTION VISUELLE EQUIPEMENT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OR004002654253</t>
+          <t>OR004002538082</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-LIMBAT-0P501A</t>
+          <t>SF01-PS-PS03-LIMBAT-0T7402</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MOTOPOMPE TRANSFRTE ACIDE P5401A</t>
+          <t>BAC DE STOCKAGE ACIDE SULFURIQUE T5401B</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>S-PC-P5401A</t>
+          <t>S-PC-T5401B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2042,14 +2038,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>IP1020260904</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>46269</v>
+        <v>46254</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2072,36 +2068,36 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13667529</v>
+        <v>13440340</v>
       </c>
       <c r="B19" t="n">
-        <v>4002751724</v>
+        <v>4002538084</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION VISUELLE CIRCUIT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OR004002751724</t>
+          <t>OR004002538084</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0P7301</t>
+          <t>SF01-PS-PS03-LIMBAT-VAPRBP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MOTOPOMPE D'ACIDE DE SECHAGE PSIII</t>
+          <t>CIRCUIT VAPEUR BP LIMITE BATTERIE PSIII</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>S-PC-P7301</t>
+          <t>S-PC-PSIII-VAPBP</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2131,21 +2127,21 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>46278</v>
+        <v>46254</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2155,44 +2151,40 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13667603</v>
+        <v>13440342</v>
       </c>
       <c r="B20" t="n">
-        <v>4002751744</v>
+        <v>4002538086</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION VISUELLE CIRCUIT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OR004002751744</t>
+          <t>OR004002538086</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7101A</t>
+          <t>SF01-PS-PS03-LIMBAT-VAPRHP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A CONDENSAT P7101A PSIII</t>
+          <t>CIRCUIT VAPEUR HP LIMITE BATTERIE PSIII</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>S-PC-P7101A</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -2220,21 +2212,21 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>46278</v>
+        <v>46254</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2244,42 +2236,42 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13667625</v>
+        <v>13440343</v>
       </c>
       <c r="B21" t="n">
-        <v>4002751766</v>
+        <v>4002538087</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>INSPECTION VISUELLE CIRCUIT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OR004002751766</t>
+          <t>OR004002538087</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7102A</t>
+          <t>SF01-PS-PS03-LIMBAT-ACIDTR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
+          <t>ACID TRANSFERT LIMITE BATTERIE PSIII</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>S-PC-P7102A</t>
+          <t>S-PC-PSIII-TACID</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2309,21 +2301,21 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260820</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>46278</v>
+        <v>46254</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2333,42 +2325,42 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13667647</v>
+        <v>13563206</v>
       </c>
       <c r="B22" t="n">
-        <v>4002751778</v>
+        <v>4002653959</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OMS_MESURE VIBRATION PALIERS</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OR004002751778</t>
+          <t>OR004002653959</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7102B</t>
+          <t>SF01-PS-PS03-SECEAU-P7105B</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE HP P7102B PSIII</t>
+          <t>MOTOPOMPE D INJECTION N2H4 P7105B PSIII</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>S-PC-P7102B</t>
+          <t>S-PC-P7105B</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2388,7 +2380,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>LANC CCRP PART RIMP TEC  TàLT</t>
+          <t>LANC CCRP PART RIMP</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2398,21 +2390,21 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>46278</v>
+        <v>46269</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2422,42 +2414,42 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13667676</v>
+        <v>13563230</v>
       </c>
       <c r="B23" t="n">
-        <v>4002751817</v>
+        <v>4002654003</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LUBRIFICATION DES PALIERS</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OR004002751817</t>
+          <t>OR004002654003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7103B</t>
+          <t>SF01-PS-PS03-SECAIR-0P7322</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE IP P7103B PSIII</t>
+          <t>MOTOPOMPE HUILE GRAISSAGE GTS PSIII</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>S-PC-P7103B</t>
+          <t>S-PC-P7322</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2487,21 +2479,21 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>46278</v>
+        <v>46269</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>OT exécution &lt;1 mois | Performance Graissage</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2511,42 +2503,42 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13667683</v>
+        <v>13563259</v>
       </c>
       <c r="B24" t="n">
-        <v>4002751825</v>
+        <v>4002654031</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RONDE INPECTION ZONE 3 ACIDE</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OR004002751825</t>
+          <t>OR004002654031</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-SECEAU-P7101A</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>MOTOPOMPE A CONDENSAT P7101A PSIII</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII</t>
+          <t>S-PC-P7101A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2576,14 +2568,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>IP1020260913</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>46278</v>
+        <v>46269</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -2605,35 +2597,37 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="n">
+        <v>13563465</v>
+      </c>
       <c r="B25" t="n">
-        <v>4153057</v>
+        <v>4002654218</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CHANGEMENT DES VANNES</t>
+          <t>CTRL FONCTIONNEMENT PALAN ELEC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OR000004153057</t>
+          <t>OR004002654218</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECGAZ-0F7301</t>
+          <t>SF01-PS-PS03-SECSSL-PALNFS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FOUR A SOUFRE PSIII</t>
+          <t>PALAN ELECTRIQUE FOSSE A SOUFRE PSIII</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S-PC-F7301</t>
+          <t>S-PC-X7303</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2653,7 +2647,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>TCLO CONF ARCO CCRP ERCT JBFI MMEf RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2663,62 +2657,68 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>FATHELLAH</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46032</v>
+        <v>46292</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>45694</v>
+        <v>46269</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="n">
+        <v>13563481</v>
+      </c>
       <c r="B26" t="n">
-        <v>4153721</v>
+        <v>4002654253</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CHANGEMENT CLAPET HV1005</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OR000004153721</t>
+          <t>OR004002654253</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECGAZ-0F7301-LAIS-VIROLE</t>
+          <t>SF01-PS-PS03-LIMBAT-0P501A</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VIROLE LIAISON FOUR-CHAUDIERE PSIII</t>
+          <t>MOTOPOMPE TRANSFRTE ACIDE P5401A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>S-PC-P5401A</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>TCLO CONF ARCO CCRP ERCT JBFI MMEf RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2746,64 +2746,66 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>FATHELLAH</t>
+          <t>IP1020260904</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45962</v>
+        <v>46291</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>45694</v>
+        <v>46269</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="n">
+        <v>13667529</v>
+      </c>
       <c r="B27" t="n">
-        <v>4167608</v>
+        <v>4002751724</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Changement de manchette fuyard</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OR000004167608</t>
+          <t>OR004002751724</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS</t>
+          <t>SF01-PS-PS03-SECACI-0P7301</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
+          <t>MOTOPOMPE D'ACIDE DE SECHAGE PSIII</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII-SSU</t>
+          <t>S-PC-P7301</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2823,7 +2825,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2833,62 +2835,68 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>45702</v>
+        <v>46278</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="n">
+        <v>13667599</v>
+      </c>
       <c r="B28" t="n">
-        <v>4167611</v>
+        <v>4002751734</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remise en état pompe</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OR000004167611</t>
+          <t>OR004002751734</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS-0P7402-ASSI</t>
+          <t>SF01-PS-PS03-SECACI-0P7304</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ASSISE POMPE PUISARD ACIDE PSIII</t>
+          <t>MOTOPOMPE D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>S-PC-P7304</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -2906,7 +2914,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2916,62 +2924,68 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>45702</v>
+        <v>46278</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="n">
+        <v>13667603</v>
+      </c>
       <c r="B29" t="n">
-        <v>4167615</v>
+        <v>4002751744</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Etanchement fuit de vapeur sur conduite</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OR000004167615</t>
+          <t>OR004002751744</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-CIRVAP-CANA</t>
+          <t>SF01-PS-PS03-SECEAU-P7101A</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CANAL VAPEUR STOCKAGE SOUFRE PSIII</t>
+          <t>MOTOPOMPE A CONDENSAT P7101A PSIII</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>S-PC-P7101A</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -2989,7 +3003,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2999,62 +3013,68 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>45702</v>
+        <v>46278</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="n">
+        <v>13667612</v>
+      </c>
       <c r="B30" t="n">
-        <v>4167616</v>
+        <v>4002751753</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Etanchement fuit d'aire AI3050</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OR000004167616</t>
+          <t>OR004002751753</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303-STRC</t>
+          <t>SF01-PS-PS03-SECEAU-P7101B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>STRUCTURE  TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE A CONDENSAT P7101B PSIII</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>S-PC-P7101B</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -3072,7 +3092,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3082,64 +3102,66 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>45702</v>
+        <v>46278</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="n">
+        <v>13667621</v>
+      </c>
       <c r="B31" t="n">
-        <v>4174741</v>
+        <v>4002751762</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Blindage de conduite d'eau F cote tour H</t>
+          <t>CTRL DU NIVEAU D'HUILE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OR000004174741</t>
+          <t>OR004002751762</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECEAU-P7102A</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-P7102A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3159,7 +3181,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3169,64 +3191,66 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="n">
+        <v>13667625</v>
+      </c>
       <c r="B32" t="n">
-        <v>4174916</v>
+        <v>4002751766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>serrage PV de la bas de tour HRS</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>OR000004174916</t>
+          <t>OR004002751766</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECEAU-P7102A</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-P7102A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3246,7 +3270,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3256,64 +3280,66 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="n">
+        <v>13667647</v>
+      </c>
       <c r="B33" t="n">
-        <v>4174995</v>
+        <v>4002751778</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Etanchement fuite cote dilueur HRS</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>OR000004174995</t>
+          <t>OR004002751778</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0M7301</t>
+          <t>SF01-PS-PS03-SECEAU-P7102B</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DILUEUR HRS M7301 PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE HP P7102B PSIII</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>S-PC-M7301</t>
+          <t>S-PC-P7102B</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3333,7 +3359,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3343,64 +3369,66 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="n">
+        <v>13667656</v>
+      </c>
       <c r="B34" t="n">
-        <v>4175458</v>
+        <v>4002751807</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>blindage de la gaine entrée tour HRS</t>
+          <t>CTRL DU NIVEAU D'HUILE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OR000004175458</t>
+          <t>OR004002751807</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7103A-GPPE-CIRREFOU</t>
+          <t>SF01-PS-PS03-SECEAU-P7103A</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CIRCUIT REFOULEMNT POMPE IP P7103A PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE IP P7103A PSIII</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>S-PC-P7103A-CR</t>
+          <t>S-PC-P7103A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3420,7 +3448,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3430,64 +3458,66 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="n">
+        <v>13667657</v>
+      </c>
       <c r="B35" t="n">
-        <v>4175609</v>
+        <v>4002751808</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>blindage de virole de la tour HRS cote A</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OR000004175609</t>
+          <t>OR004002751808</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECAIR-0K7301-SOUF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>GROUPE SOUFFLANTE TURBOSOUFFLANTE PSIII</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-KS7301</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3507,7 +3537,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3517,64 +3547,66 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="n">
+        <v>13667658</v>
+      </c>
       <c r="B36" t="n">
-        <v>4177040</v>
+        <v>4002751809</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Etanchement fuit d'acide sur analyseur</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OR000004177040</t>
+          <t>OR004002751809</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECEAU-P7103A</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE IP P7103A PSIII</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-P7103A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3594,7 +3626,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3604,64 +3636,66 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="n">
+        <v>13667671</v>
+      </c>
       <c r="B37" t="n">
-        <v>4177048</v>
+        <v>4002751812</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Etanchement fuite d'acide sur circuit de</t>
+          <t>OMS_MESURE VIBRATION PALIERS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OR000004177048</t>
+          <t>OR004002751812</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-CIRHRS</t>
+          <t>SF01-PS-PS03-SECEAU-P7103A</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CIRCUIT D'ACIDE HRS  PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE IP P7103A PSIII</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>S-PC-PSIII-ACIDHRS</t>
+          <t>S-PC-P7103A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3681,7 +3715,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3691,62 +3725,68 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="n">
+        <v>13667676</v>
+      </c>
       <c r="B38" t="n">
-        <v>4177135</v>
+        <v>4002751817</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>etanchement fuite sur circuit de renforc</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OR000004177135</t>
+          <t>OR004002751817</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-ACIREN</t>
+          <t>SF01-PS-PS03-SECEAU-P7103B</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CIRCUIT D'ACIDE DE RENFOCAGE PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE IP P7103B PSIII</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>S-PC-P7103B</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -3764,7 +3804,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3774,64 +3814,66 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="n">
+        <v>13667683</v>
+      </c>
       <c r="B39" t="n">
-        <v>4177269</v>
+        <v>4002751825</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>blindage de la fuite de gaz la gaine ent</t>
+          <t>RONDE INPECTION ZONE 3 ACIDE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OR000004177269</t>
+          <t>OR004002751825</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>ATELIER SULFURIQUE PS3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>SA-PC-PSIII</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3851,7 +3893,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3861,62 +3903,68 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="n">
+        <v>13667684</v>
+      </c>
       <c r="B40" t="n">
-        <v>4178642</v>
+        <v>4002751826</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>controle de la pompe</t>
+          <t>RONDE INPECTION ZONE 4 GAZ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OR000004178642</t>
+          <t>OR004002751826</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7104A-GPPE</t>
+          <t>SF01-PS-PS03</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GROUPE POMPE DOSEUSE NA3PO4 P7104A</t>
+          <t>ATELIER SULFURIQUE PS3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -3934,7 +3982,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3944,64 +3992,66 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>45705</v>
+        <v>46278</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="n">
+        <v>13667697</v>
+      </c>
       <c r="B41" t="n">
-        <v>4183291</v>
+        <v>4002751848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remise en état de la pompe P7305B</t>
+          <t>LUBRIFICATION DES PALIERS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OR000004183291</t>
+          <t>OR004002751848</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-P7305B</t>
+          <t>SF01-PS-PS03-SECSAS-P7401B</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
+          <t>MOTOPOMPE TRANSFRTE ACIDE P7401B</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>S-PC-P7305B</t>
+          <t>S-PC-P7401B</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4021,7 +4071,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>LANC CCRP PART RIMP TEC  TàLT</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4031,64 +4081,64 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>IP1020260913</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>45708</v>
+        <v>46278</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>OT_COR_EGAL</t>
+          <t>OT exécution &lt;1 mois | Performance Graissage</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Agent de Saisie</t>
+          <t>Chef d'Atelier</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+          <t>Exécuter les ordres lancés conformément au planning hebdomadaire validé. | Assurer la réalisation complète des tournées de graissage hebdomadaires prévues.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>4183528</v>
+        <v>4153057</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serrage boulons du moteur électrique</t>
+          <t>CHANGEMENT DES VANNES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>OR000004183528</t>
+          <t>OR000004153057</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-P7305B</t>
+          <t>SF01-PS-PS03-SECGAZ-0F7301</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
+          <t>FOUR A SOUFRE PSIII</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>S-PC-P7305B</t>
+          <t>S-PC-F7301</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4108,7 +4158,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>TCLO CONF ARCO CCRP ERCT JBFI MMEf RIMP</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4118,14 +4168,14 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>FATHELLAH</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46289</v>
+        <v>46032</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>45708</v>
+        <v>45694</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -4149,26 +4199,26 @@
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>4183608</v>
+        <v>4153721</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montage d'analyseur du soufre</t>
+          <t>CHANGEMENT CLAPET HV1005</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OR000004183608</t>
+          <t>OR000004153721</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-0T7202-CANA</t>
+          <t>SF01-PS-PS03-SECGAZ-0F7301-LAIS-VIROLE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CANAL ACESSOIR BAC SOUFRE T7202  PSIII</t>
+          <t>VIROLE LIAISON FOUR-CHAUDIERE PSIII</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4191,7 +4241,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+          <t>TCLO CONF ARCO CCRP ERCT JBFI MMEf RIMP</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4201,14 +4251,14 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>MATAR1</t>
+          <t>FATHELLAH</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46289</v>
+        <v>45962</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>45708</v>
+        <v>45694</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -4232,33 +4282,33 @@
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>4185384</v>
+        <v>4167608</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Etanchement fuite d'acide sur circuit 13</t>
+          <t>Changement de manchette fuyard</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OR000004185384</t>
+          <t>OR000004167608</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS-CIRACS</t>
+          <t>SF01-PS-PS03-SECSAS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CIRCUIT ACIDE STOCKAGE ACICE SULFURIC</t>
+          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>S-PC-PSIII-TACID</t>
+          <t>SA-PC-PSIII-SSU</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4295,7 +4345,7 @@
         <v>46289</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>45709</v>
+        <v>45702</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -4319,35 +4369,31 @@
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>4185388</v>
+        <v>4167611</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Préparation manchette  fuyard FT1318</t>
+          <t>Remise en état pompe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OR000004185388</t>
+          <t>OR000004167611</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS-CIRACS</t>
+          <t>SF01-PS-PS03-SECSAS-0P7402-ASSI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CIRCUIT ACIDE STOCKAGE ACICE SULFURIC</t>
+          <t>ASSISE POMPE PUISARD ACIDE PSIII</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>S-PC-PSIII-TACID</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -4382,7 +4428,7 @@
         <v>46289</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>45709</v>
+        <v>45702</v>
       </c>
       <c r="R45" t="n">
         <v>1</v>
@@ -4406,35 +4452,31 @@
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>4185476</v>
+        <v>4167615</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Contrôle douche de sécurité cote HRS</t>
+          <t>Etanchement fuit de vapeur sur conduite</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OR000004185476</t>
+          <t>OR000004167615</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECSSL-CIRVAP-CANA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>CANAL VAPEUR STOCKAGE SOUFRE PSIII</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>S-PC-C7303</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -4469,7 +4511,7 @@
         <v>46289</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>45709</v>
+        <v>45702</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -4493,26 +4535,26 @@
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>4185587</v>
+        <v>4167616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Etanchement fuite sur serpentin d'eau de</t>
+          <t>Etanchement fuit d'aire AI3050</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>OR000004185587</t>
+          <t>OR000004167616</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-CIRVAP</t>
+          <t>SF01-PS-PS03-SECACI-0C7303-STRC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CIRCUIT DE VAPEUR STOCKAGE SOUFRE PSIII</t>
+          <t>STRUCTURE  TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4552,7 +4594,7 @@
         <v>46289</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>45709</v>
+        <v>45702</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -4574,37 +4616,35 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>10148439</v>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>4185594</v>
+        <v>4174741</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Etanchement fuite sur circuit de décharg</t>
+          <t>Blindage de conduite d'eau F cote tour H</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>OR000004185594</t>
+          <t>OR000004174741</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7103A</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE IP P7103A PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>S-PC-P7103A</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4641,7 +4681,7 @@
         <v>46289</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>45709</v>
+        <v>45705</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -4665,33 +4705,33 @@
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>4185841</v>
+        <v>4174916</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Changement manchette fuyard sur 1318</t>
+          <t>serrage PV de la bas de tour HRS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OR000004185841</t>
+          <t>OR000004174916</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII-SSU</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4728,7 +4768,7 @@
         <v>46289</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>45709</v>
+        <v>45705</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -4752,33 +4792,33 @@
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>4189717</v>
+        <v>4174995</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montage vanne VH</t>
+          <t>Etanchement fuite cote dilueur HRS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OR000004189717</t>
+          <t>OR000004174995</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECAIR-0K7301</t>
+          <t>SF01-PS-PS03-SECACI-0M7301</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TURBOSOUFFLANTE PSIII</t>
+          <t>DILUEUR HRS M7301 PSIII</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>S-PC-K7301</t>
+          <t>S-PC-M7301</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4815,7 +4855,7 @@
         <v>46289</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>45712</v>
+        <v>45705</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -4839,33 +4879,33 @@
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>4191059</v>
+        <v>4175458</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Démontage clapet de la pompe P7401/B</t>
+          <t>blindage de la gaine entrée tour HRS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OR000004191059</t>
+          <t>OR000004175458</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS-P7401B</t>
+          <t>SF01-PS-PS03-SECEAU-P7103A-GPPE-CIRREFOU</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MOTOPOMPE TRANSFRTE ACIDE P7401B</t>
+          <t>CIRCUIT REFOULEMNT POMPE IP P7103A PSIII</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>S-PC-P7401B</t>
+          <t>S-PC-P7103A-CR</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4902,7 +4942,7 @@
         <v>46289</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>45712</v>
+        <v>45705</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -4924,37 +4964,35 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>10150502</v>
-      </c>
+      <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>4198357</v>
+        <v>4175609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Changement de la pompe à soufre P7305/B</t>
+          <t>blindage de virole de la tour HRS cote A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OR000004198357</t>
+          <t>OR000004175609</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-P7305B</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>S-PC-P7305B</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4991,7 +5029,7 @@
         <v>46289</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>45713</v>
+        <v>45705</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -5015,33 +5053,33 @@
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>4198678</v>
+        <v>4177040</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Changement vanne de purge</t>
+          <t>Etanchement fuit d'acide sur analyseur</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OR000004198678</t>
+          <t>OR000004177040</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECAIR-0K7301-TURB</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GROUPE TURBINE TURBOSOUFFLANTE PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>S-PC-KT 7301</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5078,7 +5116,7 @@
         <v>46289</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>45713</v>
+        <v>45705</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -5102,33 +5140,33 @@
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>4198882</v>
+        <v>4177048</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>remise en état de la pompe P7104/C</t>
+          <t>Etanchement fuite d'acide sur circuit de</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OR000004198882</t>
+          <t>OR000004177048</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7104C</t>
+          <t>SF01-PS-PS03-SECACI-CIRHRS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MOTOPOMPE INJECTION NA3PO4 P7104C PSIII</t>
+          <t>CIRCUIT D'ACIDE HRS  PSIII</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>S-PC-P7104C</t>
+          <t>S-PC-PSIII-ACIDHRS</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5165,7 +5203,7 @@
         <v>46289</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>45713</v>
+        <v>45705</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -5187,39 +5225,33 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>10159772</v>
-      </c>
+      <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>4198890</v>
+        <v>4177135</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fuite sur la vanne de purge</t>
+          <t>etanchement fuite sur circuit de renforc</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OR000004198890</t>
+          <t>OR000004177135</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-SECACI-ACIREN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>CIRCUIT D'ACIDE DE RENFOCAGE PSIII</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>SA-PC-PSIII</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -5254,7 +5286,7 @@
         <v>46289</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>45713</v>
+        <v>45705</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -5278,16 +5310,16 @@
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>4199970</v>
+        <v>4177269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Etanchement fuite eau sanitaire</t>
+          <t>blindage de la fuite de gaz la gaine ent</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OR000004199970</t>
+          <t>OR000004177269</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5341,7 +5373,7 @@
         <v>46289</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>45714</v>
+        <v>45705</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
@@ -5365,35 +5397,31 @@
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>4199978</v>
+        <v>4178642</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Etanchement fuite eau dilution</t>
+          <t>controle de la pompe</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OR000004199978</t>
+          <t>OR000004178642</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECEAU-P7104A-GPPE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>GROUPE POMPE DOSEUSE NA3PO4 P7104A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>S-PC-C7303</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -5428,7 +5456,7 @@
         <v>46289</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>45714</v>
+        <v>45705</v>
       </c>
       <c r="R57" t="n">
         <v>1</v>
@@ -5452,31 +5480,35 @@
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>4200041</v>
+        <v>4183291</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serrage des boulons sur circuit de vidan</t>
+          <t>Remise en état de la pompe P7305B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OR000004200041</t>
+          <t>OR000004183291</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0P7303-TRAN</t>
+          <t>SF01-PS-PS03-SECSSL-P7305B</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TRANSMISSION VIDANGE D'ACIDE PSIII</t>
+          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>S-PC-P7305B</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -5511,7 +5543,7 @@
         <v>46289</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>45714</v>
+        <v>45708</v>
       </c>
       <c r="R58" t="n">
         <v>1</v>
@@ -5535,33 +5567,33 @@
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>4200049</v>
+        <v>4183528</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Démontage et remontage pompe puisard</t>
+          <t>Serrage boulons du moteur électrique</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OR000004200049</t>
+          <t>OR000004183528</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS-0P7402</t>
+          <t>SF01-PS-PS03-SECSSL-P7305B</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MOTOPOMPE PUISARD P7402</t>
+          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>S-PC-P7402</t>
+          <t>S-PC-P7305B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5598,7 +5630,7 @@
         <v>46289</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>45714</v>
+        <v>45708</v>
       </c>
       <c r="R59" t="n">
         <v>1</v>
@@ -5620,39 +5652,33 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>10148387</v>
-      </c>
+      <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>4202405</v>
+        <v>4183608</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remise en état de la pompe  7305/B</t>
+          <t>Montage d'analyseur du soufre</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>OR000004202405</t>
+          <t>OR000004183608</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-P7305B</t>
+          <t>SF01-PS-PS03-SECSSL-0T7202-CANA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
+          <t>CANAL ACESSOIR BAC SOUFRE T7202  PSIII</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>S-PC-P7305B</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -5687,7 +5713,7 @@
         <v>46289</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>45714</v>
+        <v>45708</v>
       </c>
       <c r="R60" t="n">
         <v>1</v>
@@ -5711,33 +5737,33 @@
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>4202419</v>
+        <v>4185384</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Changement manchette fuyard acide</t>
+          <t>Etanchement fuite d'acide sur circuit 13</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>OR000004202419</t>
+          <t>OR000004185384</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS</t>
+          <t>SF01-PS-PS03-SECSAS-CIRACS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
+          <t>CIRCUIT ACIDE STOCKAGE ACICE SULFURIC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII-SSU</t>
+          <t>S-PC-PSIII-TACID</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5774,7 +5800,7 @@
         <v>46289</v>
       </c>
       <c r="Q61" s="2" t="n">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="R61" t="n">
         <v>1</v>
@@ -5796,37 +5822,35 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>10150537</v>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>4202462</v>
+        <v>4185388</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Changement de la pompe P7305/B</t>
+          <t>Préparation manchette  fuyard FT1318</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OR000004202462</t>
+          <t>OR000004185388</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-P7305B</t>
+          <t>SF01-PS-PS03-SECSAS-CIRACS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
+          <t>CIRCUIT ACIDE STOCKAGE ACICE SULFURIC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>S-PC-P7305B</t>
+          <t>S-PC-PSIII-TACID</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5863,7 +5887,7 @@
         <v>46289</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="R62" t="n">
         <v>1</v>
@@ -5887,33 +5911,33 @@
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>4202467</v>
+        <v>4185476</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remise en état de la pompe P7102/C</t>
+          <t>Contrôle douche de sécurité cote HRS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OR000004202467</t>
+          <t>OR000004185476</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7102C</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TURBO POMPE ALIMENTAIRE P7102C PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>S-PC-P7102C</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5950,7 +5974,7 @@
         <v>46289</v>
       </c>
       <c r="Q63" s="2" t="n">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="R63" t="n">
         <v>1</v>
@@ -5974,35 +5998,31 @@
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>4202596</v>
+        <v>4185587</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serrage châssis de la pompe P7102/A</t>
+          <t>Etanchement fuite sur serpentin d'eau de</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OR000004202596</t>
+          <t>OR000004185587</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7102A</t>
+          <t>SF01-PS-PS03-SECSSL-CIRVAP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
+          <t>CIRCUIT DE VAPEUR STOCKAGE SOUFRE PSIII</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>S-PC-P7102A</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -6037,7 +6057,7 @@
         <v>46289</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="R64" t="n">
         <v>1</v>
@@ -6059,35 +6079,37 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="n">
+        <v>10148439</v>
+      </c>
       <c r="B65" t="n">
-        <v>4202712</v>
+        <v>4185594</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Démontage monorail de la soufflante</t>
+          <t>Etanchement fuite sur circuit de décharg</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OR000004202712</t>
+          <t>OR000004185594</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECAIR-0K7301</t>
+          <t>SF01-PS-PS03-SECEAU-P7103A</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TURBOSOUFFLANTE PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE IP P7103A PSIII</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>S-PC-K7301</t>
+          <t>S-PC-P7103A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6124,7 +6146,7 @@
         <v>46289</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="R65" t="n">
         <v>1</v>
@@ -6148,33 +6170,33 @@
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>4202767</v>
+        <v>4185841</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montage caillebotis au niveau de canivea</t>
+          <t>Changement manchette fuyard sur 1318</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OR000004202767</t>
+          <t>OR000004185841</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECSAS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>SA-PC-PSIII-SSU</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6211,7 +6233,7 @@
         <v>46289</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="R66" t="n">
         <v>1</v>
@@ -6235,31 +6257,35 @@
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>4203794</v>
+        <v>4189717</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montage des bras des vannes d'analyseur</t>
+          <t>Montage vanne VH</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OR000004203794</t>
+          <t>OR000004189717</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-0T7307-STRC</t>
+          <t>SF01-PS-PS03-SECAIR-0K7301</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>STRUCTURE FOSSE A SOUFRE ATELIER PSIII</t>
+          <t>TURBOSOUFFLANTE PSIII</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>S-PC-K7301</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -6294,7 +6320,7 @@
         <v>46289</v>
       </c>
       <c r="Q67" s="2" t="n">
-        <v>45715</v>
+        <v>45712</v>
       </c>
       <c r="R67" t="n">
         <v>1</v>
@@ -6318,33 +6344,33 @@
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>4203983</v>
+        <v>4191059</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Etanchement fuite sur l'analyseur AI3000</t>
+          <t>Démontage clapet de la pompe P7401/B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OR000004203983</t>
+          <t>OR000004191059</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECSAS-P7401B</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE TRANSFRTE ACIDE P7401B</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-P7401B</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -6381,7 +6407,7 @@
         <v>46289</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>45715</v>
+        <v>45712</v>
       </c>
       <c r="R68" t="n">
         <v>1</v>
@@ -6404,34 +6430,38 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>10148480</v>
+        <v>10150502</v>
       </c>
       <c r="B69" t="n">
-        <v>4205200</v>
+        <v>4198357</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Changement buse d'atomiseur B</t>
+          <t>Changement de la pompe à soufre P7305/B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>OR000004205200</t>
+          <t>OR000004198357</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECGAZ-0F7302-CANA</t>
+          <t>SF01-PS-PS03-SECSSL-P7305B</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ACCESSOIRE BRULEUR PILLARD FOUR SOUFRE</t>
+          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>S-PC-P7305B</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -6466,7 +6496,7 @@
         <v>46289</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>45715</v>
+        <v>45713</v>
       </c>
       <c r="R69" t="n">
         <v>1</v>
@@ -6488,37 +6518,35 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>10148482</v>
-      </c>
+      <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>4205226</v>
+        <v>4198678</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Etanchement fuite de gaz sur E.G.G.C</t>
+          <t>Changement vanne de purge</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>OR000004205226</t>
+          <t>OR000004198678</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECGAZ-0E7316</t>
+          <t>SF01-PS-PS03-SECAIR-0K7301-TURB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ECHANGEUR GAZ-GAZ CHAUD E7316 PSIII</t>
+          <t>GROUPE TURBINE TURBOSOUFFLANTE PSIII</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>S-PC-E7316</t>
+          <t>S-PC-KT 7301</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6555,7 +6583,7 @@
         <v>46289</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>45715</v>
+        <v>45713</v>
       </c>
       <c r="R70" t="n">
         <v>1</v>
@@ -6579,33 +6607,33 @@
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>4205255</v>
+        <v>4198882</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Changement volant de la vanne de circuit</t>
+          <t>remise en état de la pompe P7104/C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OR000004205255</t>
+          <t>OR000004198882</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS</t>
+          <t>SF01-PS-PS03-SECEAU-P7104C</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
+          <t>MOTOPOMPE INJECTION NA3PO4 P7104C PSIII</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII-SSU</t>
+          <t>S-PC-P7104C</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6642,7 +6670,7 @@
         <v>46289</v>
       </c>
       <c r="Q71" s="2" t="n">
-        <v>45715</v>
+        <v>45713</v>
       </c>
       <c r="R71" t="n">
         <v>1</v>
@@ -6665,36 +6693,36 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>10148319</v>
+        <v>10159772</v>
       </c>
       <c r="B72" t="n">
-        <v>4205291</v>
+        <v>4198890</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remise en état clapet anti retour 7401</t>
+          <t>Fuite sur la vanne de purge</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>OR000004205291</t>
+          <t>OR000004198890</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSAS-P7401B</t>
+          <t>SF01-PS-PS03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MOTOPOMPE TRANSFRTE ACIDE P7401B</t>
+          <t>ATELIER SULFURIQUE PS3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>S-PC-P7401B</t>
+          <t>SA-PC-PSIII</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6731,7 +6759,7 @@
         <v>46289</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>45715</v>
+        <v>45713</v>
       </c>
       <c r="R72" t="n">
         <v>1</v>
@@ -6755,33 +6783,33 @@
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>4205320</v>
+        <v>4199970</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Etanchement fuite eau alimentaire</t>
+          <t>Etanchement fuite eau sanitaire</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>OR000004205320</t>
+          <t>OR000004199970</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-LIMBAT-EAUALI</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CIR EAU ALIMENTAIRE LIMIT BATTERIE PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>S-PC-PSIII-EAUIP</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6818,7 +6846,7 @@
         <v>46289</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="R73" t="n">
         <v>1</v>
@@ -6840,20 +6868,18 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>10165985</v>
-      </c>
+      <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>4205348</v>
+        <v>4199978</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Etanchement fuite d'acide sur le virole</t>
+          <t>Etanchement fuite eau dilution</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>OR000004205348</t>
+          <t>OR000004199978</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6907,7 +6933,7 @@
         <v>46289</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="R74" t="n">
         <v>1</v>
@@ -6931,35 +6957,31 @@
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>4205358</v>
+        <v>4200041</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Etanchement fuite sur prise pression gaz</t>
+          <t>Serrage des boulons sur circuit de vidan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OR000004205358</t>
+          <t>OR000004200041</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECGAZ</t>
+          <t>SF01-PS-PS03-SECACI-0P7303-TRAN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SECTION GAZ DE L'ATELIER PSIII</t>
+          <t>TRANSMISSION VIDANGE D'ACIDE PSIII</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>S-PC-PSIII-GAZ</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -6994,7 +7016,7 @@
         <v>46289</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="R75" t="n">
         <v>1</v>
@@ -7016,37 +7038,35 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>10148435</v>
-      </c>
+      <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>4205434</v>
+        <v>4200049</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Etanchement fuite d'acide sur le vidange</t>
+          <t>Démontage et remontage pompe puisard</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>OR000004205434</t>
+          <t>OR000004200049</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECSAS-0P7402</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE PUISARD P7402</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-P7402</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7080,10 +7100,10 @@
         </is>
       </c>
       <c r="P76" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="R76" t="n">
         <v>1</v>
@@ -7105,35 +7125,37 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="n">
+        <v>10148387</v>
+      </c>
       <c r="B77" t="n">
-        <v>4205509</v>
+        <v>4202405</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>d2MONTAGE ET REMONTAGE FILTRE EAU FILTRE</t>
+          <t>Remise en état de la pompe  7305/B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OR000004205509</t>
+          <t>OR000004202405</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-LIMBAT-EAUFIL</t>
+          <t>SF01-PS-PS03-SECSSL-P7305B</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CIRCUIT EAU FILTREE LIMIT BATTERIE PSIII</t>
+          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>S-PC-PSIII-EAUFT</t>
+          <t>S-PC-P7305B</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7167,10 +7189,10 @@
         </is>
       </c>
       <c r="P77" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>45715</v>
+        <v>45714</v>
       </c>
       <c r="R77" t="n">
         <v>1</v>
@@ -7194,31 +7216,35 @@
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>4206175</v>
+        <v>4202419</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remise en état marche escalier fosse</t>
+          <t>Changement manchette fuyard acide</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OR000004206175</t>
+          <t>OR000004202419</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECSSL-0T7307-MOAC</t>
+          <t>SF01-PS-PS03-SECSAS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MOYENS ACCES FOSSE SOUFRE ATELIER PSIII</t>
+          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII-SSU</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -7250,10 +7276,10 @@
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>45716</v>
+        <v>45714</v>
       </c>
       <c r="R78" t="n">
         <v>1</v>
@@ -7275,35 +7301,37 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="n">
+        <v>10150537</v>
+      </c>
       <c r="B79" t="n">
-        <v>4206264</v>
+        <v>4202462</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Contrôle des vannes d'échantillons acide</t>
+          <t>Changement de la pompe P7305/B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>OR000004206264</t>
+          <t>OR000004202462</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECSSL-P7305B</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>MOTOPOMPE A SOUFRE P7305B PSIII</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-P7305B</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -7337,10 +7365,10 @@
         </is>
       </c>
       <c r="P79" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>45716</v>
+        <v>45714</v>
       </c>
       <c r="R79" t="n">
         <v>1</v>
@@ -7364,33 +7392,33 @@
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>4206275</v>
+        <v>4202467</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serrage des boulons de la pompe ELEC</t>
+          <t>Remise en état de la pompe P7102/C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>OR000004206275</t>
+          <t>OR000004202467</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECAIR-0K7301</t>
+          <t>SF01-PS-PS03-SECEAU-P7102C</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TURBOSOUFFLANTE PSIII</t>
+          <t>TURBO POMPE ALIMENTAIRE P7102C PSIII</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>S-PC-K7301</t>
+          <t>S-PC-P7102C</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -7424,10 +7452,10 @@
         </is>
       </c>
       <c r="P80" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>45716</v>
+        <v>45714</v>
       </c>
       <c r="R80" t="n">
         <v>1</v>
@@ -7451,31 +7479,35 @@
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>4208334</v>
+        <v>4202596</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Etanchement fuite sur entonnoir acide</t>
+          <t>Serrage châssis de la pompe P7102/A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OR000004208334</t>
+          <t>OR000004202596</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI</t>
+          <t>SF01-PS-PS03-SECEAU-P7102A</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SECTION ACIDE DE L'ATELIER PSIII</t>
+          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>S-PC-P7102A</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -7507,10 +7539,10 @@
         </is>
       </c>
       <c r="P81" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="R81" t="n">
         <v>1</v>
@@ -7532,37 +7564,35 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>10148483</v>
-      </c>
+      <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>4208531</v>
+        <v>4202712</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>changement vanne prise de pression</t>
+          <t>Démontage monorail de la soufflante</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OR000004208531</t>
+          <t>OR000004202712</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECACI-0C7303</t>
+          <t>SF01-PS-PS03-SECAIR-0K7301</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>TOUR D'ACIDE HRS PSIII</t>
+          <t>TURBOSOUFFLANTE PSIII</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>S-PC-C7303</t>
+          <t>S-PC-K7301</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7596,10 +7626,10 @@
         </is>
       </c>
       <c r="P82" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>45717</v>
+        <v>45714</v>
       </c>
       <c r="R82" t="n">
         <v>1</v>
@@ -7621,37 +7651,35 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>10148430</v>
-      </c>
+      <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>4210207</v>
+        <v>4202767</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>remise en état P7102A</t>
+          <t>Montage caillebotis au niveau de canivea</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OR000004210207</t>
+          <t>OR000004202767</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7102A</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>S-PC-P7102A</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7685,10 +7713,10 @@
         </is>
       </c>
       <c r="P83" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>45719</v>
+        <v>45714</v>
       </c>
       <c r="R83" t="n">
         <v>1</v>
@@ -7712,35 +7740,31 @@
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>4219047</v>
+        <v>4203794</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>changement manchette fuyard E/F</t>
+          <t>Montage des bras des vannes d'analyseur</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OR000004219047</t>
+          <t>OR000004203794</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-LIMBAT-EAUFIL</t>
+          <t>SF01-PS-PS03-SECSSL-0T7307-STRC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CIRCUIT EAU FILTREE LIMIT BATTERIE PSIII</t>
+          <t>STRUCTURE FOSSE A SOUFRE ATELIER PSIII</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>S-PC-PSIII-EAUFT</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -7772,10 +7796,10 @@
         </is>
       </c>
       <c r="P84" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>45721</v>
+        <v>45715</v>
       </c>
       <c r="R84" t="n">
         <v>1</v>
@@ -7799,33 +7823,33 @@
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>4219051</v>
+        <v>4203983</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Démontage et remontage filtre eau de mer</t>
+          <t>Etanchement fuite sur l'analyseur AI3000</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OR000004219051</t>
+          <t>OR000004203983</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEMR-S7306A</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FILTRE A EAU DE MER S7306A PSIII</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>S-PC-S7306A</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7859,10 +7883,10 @@
         </is>
       </c>
       <c r="P85" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>45721</v>
+        <v>45715</v>
       </c>
       <c r="R85" t="n">
         <v>1</v>
@@ -7885,38 +7909,34 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>13752051</v>
+        <v>10148480</v>
       </c>
       <c r="B86" t="n">
-        <v>4002840947</v>
+        <v>4205200</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>étanchement fuite d'huile sur palier P71</t>
+          <t>Changement buse d'atomiseur B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>OR004002840947</t>
+          <t>OR000004205200</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03-SECEAU-P7102B</t>
+          <t>SF01-PS-PS03-SECGAZ-0F7302-CANA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>MOTOPOMPE ALIMENTAIRE HP P7102B PSIII</t>
+          <t>ACCESSOIRE BRULEUR PILLARD FOUR SOUFRE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>S-PC-P7102B</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>SF1-MPS3</t>
@@ -7944,14 +7964,14 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>BENMOUSSA1</t>
+          <t>MATAR1</t>
         </is>
       </c>
       <c r="P86" s="2" t="n">
         <v>46289</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>46289</v>
+        <v>45715</v>
       </c>
       <c r="R86" t="n">
         <v>1</v>
@@ -7974,36 +7994,36 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>13765250</v>
+        <v>10148482</v>
       </c>
       <c r="B87" t="n">
-        <v>4002841184</v>
+        <v>4205226</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>fixation des caillebotis prés du FEM</t>
+          <t>Etanchement fuite de gaz sur E.G.G.C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OR004002841184</t>
+          <t>OR000004205226</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-SECGAZ-0E7316</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>ECHANGEUR GAZ-GAZ CHAUD E7316 PSIII</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII</t>
+          <t>S-PC-E7316</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8040,7 +8060,7 @@
         <v>46289</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>46289</v>
+        <v>45715</v>
       </c>
       <c r="R87" t="n">
         <v>1</v>
@@ -8064,33 +8084,33 @@
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>4002850071</v>
+        <v>4205255</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remise en état circuit de remplissage de</t>
+          <t>Changement volant de la vanne de circuit</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OR004002850071</t>
+          <t>OR000004205255</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-SECSAS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>STOCKAGE ACIDE SULFURIQUE ATELIER PSIII</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII</t>
+          <t>SA-PC-PSIII-SSU</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -8124,10 +8144,10 @@
         </is>
       </c>
       <c r="P88" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>46290</v>
+        <v>45715</v>
       </c>
       <c r="R88" t="n">
         <v>1</v>
@@ -8149,35 +8169,37 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="n">
+        <v>10148319</v>
+      </c>
       <c r="B89" t="n">
-        <v>4002850075</v>
+        <v>4205291</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serrage palier de la pompe HP</t>
+          <t>Remise en état clapet anti retour 7401</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OR004002850075</t>
+          <t>OR000004205291</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-SECSAS-P7401B</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>MOTOPOMPE TRANSFRTE ACIDE P7401B</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII</t>
+          <t>S-PC-P7401B</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -8211,10 +8233,10 @@
         </is>
       </c>
       <c r="P89" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>46290</v>
+        <v>45715</v>
       </c>
       <c r="R89" t="n">
         <v>1</v>
@@ -8238,33 +8260,33 @@
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>4002850222</v>
+        <v>4205320</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Intalation vanne pour etanchement fuite</t>
+          <t>Etanchement fuite eau alimentaire</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>OR004002850222</t>
+          <t>OR000004205320</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-LIMBAT-EAUALI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>CIR EAU ALIMENTAIRE LIMIT BATTERIE PSIII</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII</t>
+          <t>S-PC-PSIII-EAUIP</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -8298,10 +8320,10 @@
         </is>
       </c>
       <c r="P90" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>46290</v>
+        <v>45715</v>
       </c>
       <c r="R90" t="n">
         <v>1</v>
@@ -8323,35 +8345,37 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="n">
+        <v>10165985</v>
+      </c>
       <c r="B91" t="n">
-        <v>4002850240</v>
+        <v>4205348</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Changement de la pompe P7103B</t>
+          <t>Etanchement fuite d'acide sur le virole</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OR004002850240</t>
+          <t>OR000004205348</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SF01-PS-PS03</t>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ATELIER SULFURIQUE PS3</t>
+          <t>TOUR D'ACIDE HRS PSIII</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SA-PC-PSIII</t>
+          <t>S-PC-C7303</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8385,10 +8409,10 @@
         </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>46290</v>
+        <v>45715</v>
       </c>
       <c r="R91" t="n">
         <v>1</v>
@@ -8404,6 +8428,1487 @@
         </is>
       </c>
       <c r="U91" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>4205358</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Etanchement fuite sur prise pression gaz</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OR000004205358</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECGAZ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SECTION GAZ DE L'ATELIER PSIII</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>S-PC-PSIII-GAZ</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>10148435</v>
+      </c>
+      <c r="B93" t="n">
+        <v>4205434</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Etanchement fuite d'acide sur le vidange</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OR000004205434</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>TOUR D'ACIDE HRS PSIII</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>S-PC-C7303</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>4205509</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>d2MONTAGE ET REMONTAGE FILTRE EAU FILTRE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OR000004205509</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-LIMBAT-EAUFIL</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CIRCUIT EAU FILTREE LIMIT BATTERIE PSIII</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>S-PC-PSIII-EAUFT</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>4206175</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remise en état marche escalier fosse</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OR000004206175</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECSSL-0T7307-MOAC</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>MOYENS ACCES FOSSE SOUFRE ATELIER PSIII</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>4206264</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Contrôle des vannes d'échantillons acide</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OR000004206264</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>TOUR D'ACIDE HRS PSIII</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>S-PC-C7303</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>4206275</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Serrage des boulons de la pompe ELEC</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OR000004206275</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECAIR-0K7301</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TURBOSOUFFLANTE PSIII</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>S-PC-K7301</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>4208334</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Etanchement fuite sur entonnoir acide</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OR000004208334</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECACI</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SECTION ACIDE DE L'ATELIER PSIII</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>10148483</v>
+      </c>
+      <c r="B99" t="n">
+        <v>4208531</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>changement vanne prise de pression</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OR000004208531</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECACI-0C7303</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TOUR D'ACIDE HRS PSIII</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>S-PC-C7303</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>45717</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>10148430</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4210207</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>remise en état P7102A</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OR000004210207</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECEAU-P7102A</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>MOTOPOMPE ALIMENTAIRE HP P7102A PSIII</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>S-PC-P7102A</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>45719</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>4219047</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>changement manchette fuyard E/F</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>OR000004219047</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-LIMBAT-EAUFIL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CIRCUIT EAU FILTREE LIMIT BATTERIE PSIII</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>S-PC-PSIII-EAUFT</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>4219051</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Démontage et remontage filtre eau de mer</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OR000004219051</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECEMR-S7306A</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>FILTRE A EAU DE MER S7306A PSIII</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>S-PC-S7306A</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>13752051</v>
+      </c>
+      <c r="B103" t="n">
+        <v>4002840947</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>étanchement fuite d'huile sur palier P71</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OR004002840947</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03-SECEAU-P7102B</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>MOTOPOMPE ALIMENTAIRE HP P7102B PSIII</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>S-PC-P7102B</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>BENMOUSSA1</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13765250</v>
+      </c>
+      <c r="B104" t="n">
+        <v>4002841184</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>fixation des caillebotis prés du FEM</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OR004002841184</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ATELIER SULFURIQUE PS3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>4002850071</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remise en état circuit de remplissage de</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OR004002850071</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ATELIER SULFURIQUE PS3</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>4002850075</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Serrage palier de la pompe HP</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OR004002850075</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ATELIER SULFURIQUE PS3</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>4002850222</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Intalation vanne pour etanchement fuite</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OR004002850222</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ATELIER SULFURIQUE PS3</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>4002850240</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Changement de la pompe P7103B</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OR004002850240</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>SF01-PS-PS03</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ATELIER SULFURIQUE PS3</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SA-PC-PSIII</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>SF1-MPS3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>GM4</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>SF01</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>TCLO CONF CCRP JBFI PART RIMP</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>SOPL</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>MATAR1</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>OT_COR_EGAL</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Agent de Saisie</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
         <is>
           <t>Contrôler la cohérence entre coûts budgétés et coûts réels, et corriger les OT dont les coûts ne sont pas cohérents (coûts réels = 0 ou égaux au budget).</t>
         </is>
